--- a/output/pdf_financials_xlsx/NWI.xlsx
+++ b/output/pdf_financials_xlsx/NWI.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.056029</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.034872</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.1933</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.056029</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.034485</v>
+        <v>0.069357</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.1933</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.056129</v>
+        <v>0.0001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.034872</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.1933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">

--- a/output/pdf_financials_xlsx/NWI.xlsx
+++ b/output/pdf_financials_xlsx/NWI.xlsx
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.000457</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.001358</v>
       </c>
     </row>
     <row r="29">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.24131</v>
+        <v>-1.24078</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.352692</v>
+        <v>-0.352235</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.263711</v>
+        <v>-0.262353</v>
       </c>
     </row>
     <row r="30">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000457</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.001358</v>
       </c>
     </row>
     <row r="101">
@@ -3761,7 +3761,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4410,7 +4414,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.00053</v>
       </c>
@@ -4811,7 +4819,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -5644,7 +5656,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.00053</v>
       </c>

--- a/output/pdf_financials_xlsx/NWI.xlsx
+++ b/output/pdf_financials_xlsx/NWI.xlsx
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.006223</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.028927</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.059456</v>
       </c>
     </row>
     <row r="116">
@@ -4003,7 +4003,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>0.028927</v>
       </c>
@@ -4354,7 +4358,11 @@
           <t>Loan accretion expense</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>0.006223</v>
       </c>
